--- a/ig/test-tabs-svs/CodeSystem-TRE-R243-CompetenceSpecifique.xlsx
+++ b/ig/test-tabs-svs/CodeSystem-TRE-R243-CompetenceSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="187">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,457 +118,463 @@
     <t>Count</t>
   </si>
   <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Maîtrise de la Langue des Signes Française (LSF)</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Maîtrise de la Langue Parlé Complété (LPC)</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Maîtrise de la lecture et de l'écriture du Braille</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Art-thérapeute</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Neuropsychologue</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Maîtrise de langue étrangère</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Maîtrise de langue régionale</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Intervenant pair (médiateur, pair-aidant)</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Maîtrise de la communication augmentative alternative</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Socio-esthéticienne</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Enseignant du 1er degré</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Enseignant du 2nd degré</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Enseignant du supérieur</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Puéricultrice</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Auxiliaire de puériculture</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Accompagnant des élèves en situation de handicap</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Aide humaine en milieu scolaire</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Maitrise de prog d'interv globaux à réf compor (ABA,...) ou dév (TEACCH,...)</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Médecin coordonnateur</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Infirmier coordonnateur</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Phoniatre</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Audio phonologue</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Ingénieur en analyse du mouvement</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Psychologue clinicien</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Animateur socio-culturel</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Moniteur d'atelier</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Maîtrise de la Méthode verbo-tonale : aide à l'apprentissage de la parole</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Maîtrise du Braille</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Maîtrise du PECS</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Maîtrise de la Méthode ABA</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Maîtrise du MAKATON</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Maîtrise des Gestes Borel-Maisonny</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Maîtrise de la COGHAMO</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Maîtrise des Codes de communication pictographiques (classeurs, planches)</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Maît des out info avc synthèse voc à entrée ortho ou picto (téléth, log de com)</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Maîtrise des log d'aide à la transcription (retour voc, prédicteur de mots)</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Ostéopathe</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Enseignant en Activité Physique Adaptée (EAPA)</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Accompagnant des Élèves en Situation de Handicap (AESH)</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Maîtrise de prog d'interv globaux à réf développementale (TEACCH, DENVER,...)</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Psychiatre</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Gériatre</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Pédopsychiatre</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Veilleur de nuit</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Assistant(e) de soins en gérontologie</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Conseillère en économie sociale et familiale (CESF)</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Aide médico psychologique (AMP)</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Auxiliaire de vie sociale (AVS)</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Accompagnant Educatif et Social (AES)</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Avéjiste</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Instructeur en locomotion</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Educateur sportif</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Conseiller en insertion professionnelle</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Coordonnateur et gestionnaire de parcours handicap</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Neuropédiatre</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Psychopédagogue</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Ergonome</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Psychologue du travail</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>Tabacologue</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Addictologue</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Conseiller conjugal et familial</t>
+  </si>
+  <si>
     <t>62</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Maîtrise de la Langue des Signes Française (LSF)</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Maîtrise de la Langue Parlé Complété (LPC)</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>Maîtrise de la lecture et de l'écriture du Braille</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Art-thérapeute</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Neuropsychologue</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Maîtrise de langue étrangère</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>Maîtrise de langue régionale</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>Intervenant pair (médiateur, pair-aidant)</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>Maîtrise de la communication augmentative alternative</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Socio-esthéticienne</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Enseignant du 1er degré</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Enseignant du 2nd degré</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Enseignant du supérieur</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Puéricultrice</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Auxiliaire de puériculture</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Accompagnant des élèves en situation de handicap</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Aide humaine en milieu scolaire</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Maitrise de prog d'interv globaux à réf compor (ABA,...) ou dév (TEACCH,...)</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Médecin coordonnateur</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Infirmier coordonnateur</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Phoniatre</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Audio phonologue</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Ingénieur en analyse du mouvement</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Psychologue clinicien</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Animateur socio-culturel</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Moniteur d'atelier</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Maîtrise de la Méthode verbo-tonale : aide à l'apprentissage de la parole</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Maîtrise du Braille</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Maîtrise du PECS</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Maîtrise de la Méthode ABA</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Maîtrise du MAKATON</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Maîtrise des Gestes Borel-Maisonny</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Maîtrise de la COGHAMO</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Maîtrise des Codes de communication pictographiques (classeurs, planches)</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>Maît des out info avc synthèse voc à entrée ortho ou picto (téléth, log de com)</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>Maîtrise des log d'aide à la transcription (retour voc, prédicteur de mots)</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>Ostéopathe</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Enseignant en Activité Physique Adaptée (EAPA)</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>Accompagnant des Élèves en Situation de Handicap (AESH)</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Maîtrise de prog d'interv globaux à réf développementale (TEACCH, DENVER,...)</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Psychiatre</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>Gériatre</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Pédopsychiatre</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>Veilleur de nuit</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>Assistant(e) de soins en gérontologie</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>Conseillère en économie sociale et familiale (CESF)</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>Aide médico psychologique (AMP)</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>Auxiliaire de vie sociale (AVS)</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>Accompagnant Educatif et Social (AES)</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>Avéjiste</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>Instructeur en locomotion</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>Educateur sportif</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>Conseiller en insertion professionnelle</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>Coordonnateur et gestionnaire de parcours handicap</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Neuropédiatre</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>Psychopédagogue</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>Ergonome</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>Psychologue du travail</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>Tabacologue</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Addictologue</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>Conseiller conjugal et familial</t>
-  </si>
-  <si>
     <t>Maîtrise du Facile à Lire et à Comprendre (FALC)</t>
+  </si>
+  <si>
+    <t>Maitrise des outils informatisés à commande oculaire</t>
   </si>
 </sst>
 </file>
@@ -984,7 +990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1738,12 +1744,24 @@
         <v>61</v>
       </c>
       <c r="B63" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="D63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="C63" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="D63" s="2"/>
+      <c r="C64" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="D64" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
